--- a/docs/Research_questions.xlsx
+++ b/docs/Research_questions.xlsx
@@ -3309,7 +3309,7 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Six adjacent models share a pooled spread of 0.007 - they cannot be reliably rank-ordered.</t>
+          <t>Five adjacent models share a pooled spread of 0.005 (corrected 2026-08-12 from a stale 'six... 0.007', which predated Gemini Pro Preview's Dynamic-L4 crawl completing 2026-08-11) - they cannot be reliably rank-ordered.</t>
         </is>
       </c>
     </row>

--- a/docs/Research_questions.xlsx
+++ b/docs/Research_questions.xlsx
@@ -1661,7 +1661,7 @@
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>No approved hypothesis (see RQ4.2).
-Descriptive only, and constrained by the noise floor: six adjacent models sit within a combined pooled spread of 0.007, smaller than their own between-instantiation SDs, so no test could reliably separate them on this data.</t>
+Descriptive only, and constrained by the noise floor: five adjacent models sit within a combined pooled spread of 0.005 (corrected 2026-08-12 from a stale 'six... 0.007', which predated Gemini Pro Preview's Dynamic-L4 crawl completing 2026-08-11), smaller than their own between-instantiation SDs, so no test could reliably separate them on this data.</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">

--- a/docs/Research_questions.xlsx
+++ b/docs/Research_questions.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>SUPPORTED IN DIRECTION - the leaked benchmark scores higher, which is the contamination-consistent result, and all three conditionings agree. Significance depends on the correction: the definition-matched co-primary reading survives Holm (0.0078-&gt;0.0156); the raw/pre-registered-primary reading does not (0.0391-&gt;0.0782).</t>
+          <t>MIXED - the leaked benchmark scores higher on all three conditionings (the contamination-consistent direction), but significance depends on the correction: the definition-matched co-primary reading survives Holm (0.0078-&gt;0.0156); the raw/pre-registered-primary reading does not (0.0391-&gt;0.0782). Report the direction agreement as the robust claim, not raw significance.</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
           <t>APPROVED H5 (RQ4): across N=5 independent instantiations of the dynamic benchmark, pairwise Kendall's tau between LLM rankings will EXCEED 0.7.
 Test: pairwise Kendall's tau across instantiations, each from a different random seed.
 The approved H5 covers the WHOLE of RQ4 - RQ4.2, RQ4.3 and RQ4.4 have no approved hypothesis of their own and are descriptive sub-questions by design.
-VERDICT: THRESHOLD NOT MET - mean pairwise tau = 0.667 at the N=4 headline scope, below the approved 0.7 criterion, and at N=4 rather than the approved N=5 for two of nine models. The score-level stability claim (SD 0.003-0.007) is separate and strong.</t>
+VERDICT: THRESHOLD NOT MET - mean pairwise tau = 0.583 at the N=4 headline scope (corrected 2026-08-12 from a stale 0.667; live rebuild after Gemini Pro Preview's Dynamic-L4 crawl completed 2026-08-11), below the approved 0.7 criterion. N=4, not the approved N=5, for both Gemini models -- checked and declined 2026-08-12, not an open gap: closing it was quantified at $9.60 (scripts/estimate_cost.py) and declined because the noise-floor mechanism predicts more data would move tau further down, not up (analysis/HYPOTHESIS_DEVIATIONS.md's H5 entry, analysis/OPEN_ITEMS.md). The score-level stability claim (SD 0.001-0.004 for most models) is separate and strong.</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>SUPPORTED IN DIRECTION. Significance depends on the correction - report the direction agreement as the robust claim.</t>
+          <t>MIXED - PLT scores higher than ULT on all three conditionings (the contamination-consistent direction), but significance depends on the correction: definition-matched survives Holm (0.0078-&gt;0.0156), raw/pre-registered-primary does not (0.0391-&gt;0.0782). Report the direction agreement as the robust claim.</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">

--- a/docs/Research_questions.xlsx
+++ b/docs/Research_questions.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -783,243 +783,243 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2-supplementary</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Mean mutation score will keep decreasing (or stay the same) from L1 to L4 across all evaluated LLMs - it will never go back up.</t>
+          <t>POST-HOC, not part of the approved pre-registered set: if a single dynamic-benchmark instantiation is itself leaked into training, inflation should follow the leaked instantiation specifically (self- or cross-model contamination), not transfer to fresh instantiations generated from the same templates.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Spearman rho between tier index and mutation score, per model and pooled.</t>
+          <t>Seen (trained instantiation) vs fresh (held-out instantiations) baseline_pass_rate, per training source (self-contamination / cross-model contamination / non-leaked control), both Qwen model sizes (1.5B, 7B).</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>All 9 canonical models show a significant negative gradient, surviving Holm correction in both families; the effect strengthens when the near-ceiling L1 tier is excluded, ruling out a ceiling artefact.</t>
+          <t>Six conditions (2 sizes x 3 training sources), epoch 30, n=150/instantiation. Self-contamination gap: 8.7pp (1.5B), 4.7pp (7B). Cross-model contamination gap: 52.7pp (1.5B), 68.0pp (7B). Non-leaked control gap: 2.3pp (1.5B), -2.3pp (7B, noise). See analysis/finetune_endpoint_table.csv.</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Spearman rho tests a monotone TREND, not the literal 'never goes back up' clause. Closed 2026-08-12 (analysis/H3_INTERPRETATION.md): 7 of 9 models satisfy the literal clause exactly; GPT-5 and GPT-5-mini each show one sub-1pp rebound at L1-&gt;L2, both already at/above 98% mutation score at that tier (near-ceiling noise).</t>
+          <t>Supplementary/robustness-replication analysis added post-hoc; not one of the six pre-registered hypotheses and not Holm-corrected alongside them. No control-relative gain computed (unlike Comparison C) -- seen/fresh/gap reported directly per condition. Cross-model conditions additionally show a held-out execution-rate decline (epoch 0 to 30: 1.5B 92.7%-&gt;63.3%, 7B 99.7%-&gt;85.3%, analysis/finetune_decline_table.csv), partially confounding their gap with a general capability cost; self-contamination conditions preserve held-out execution rate.</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>SUPPORTED (trend) - the cleanest result in the project. Literal non-rebound clause holds for 7 of 9 models; 2 (GPT-5, GPT-5-mini) show one sub-1pp near-ceiling rebound each at L1-&gt;L2.</t>
+          <t>SUPPLEMENTARY - pattern holds under both self- and cross-model contamination: trained-instantiation scores rise, fresh-instantiation scores do not, at both model sizes. Non-leaked control shows no such gap. Strengthens H2's second-clause reading that memorisation binds to the leaked artefact, not the benchmark.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>RQ3</t>
+          <t>RQ2</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>The gap between static and dynamic mutation scores will be larger at L1-L2 than at L3-L4.</t>
+          <t>Mean mutation score will keep decreasing (or stay the same) from L1 to L4 across all evaluated LLMs - it will never go back up.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Tier x benchmark interaction in a regression treating LLM as a random effect.</t>
+          <t>Spearman rho between tier index and mutation score, per model and pooled.</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Not built. No mixed-effects model was implemented and statsmodels was deliberately not added as a dependency.</t>
+          <t>All 9 canonical models show a significant negative gradient, surviving Holm correction in both families; the effect strengthens when the near-ceiling L1 tier is excluded, ruling out a ceiling artefact.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>None - the drop is correct against the approved wording, not a shortcut. The approved text requires a static score at L1-L2; ULT/PLT contain only CC&gt;=8 functions, so no such score exists and no gap can be formed.</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>DROPPED - untestable by construction. Supervisor sign-off 2026-08-05. The reason is itself reportable: a CC-filtered static benchmark cannot speak to low-complexity behaviour.</t>
+          <t>Spearman rho tests a monotone TREND, not the literal 'never goes back up' clause. Closed 2026-08-12 (analysis/H3_INTERPRETATION.md): 7 of 9 models satisfy the literal clause exactly; GPT-5 and GPT-5-mini each show one sub-1pp rebound at L1-&gt;L2, both already at/above 98% mutation score at that tier (near-ceiling noise).</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>SUPPORTED (trend) - the cleanest result in the project. Literal non-rebound clause holds for 7 of 9 models; 2 (GPT-5, GPT-5-mini) show one sub-1pp near-ceiling rebound each at L1-&gt;L2.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="105" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>RQ3</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>The gap between static and dynamic mutation scores will be larger at L1-L2 than at L3-L4.</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Tier x benchmark interaction in a regression treating LLM as a random effect.</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Not built. No mixed-effects model was implemented and statsmodels was deliberately not added as a dependency.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>None - the drop is correct against the approved wording, not a shortcut. The approved text requires a static score at L1-L2; ULT/PLT contain only CC&gt;=8 functions, so no such score exists and no gap can be formed.</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>DROPPED - untestable by construction. Supervisor sign-off 2026-08-05. The reason is itself reportable: a CC-filtered static benchmark cannot speak to low-complexity behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="105" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
           <t>H5</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>RQ4 (all)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Across N=5 independent instantiations, pairwise Kendall's tau between LLM rankings will EXCEED 0.7.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Pairwise Kendall's tau across instantiations, each from a different random seed.</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Mean pairwise tau = 0.583 at the N=4 headline scope (corrected 2026-08-12 from a stale 0.667 -- see analysis/WORKBOOK_VERIFICATION.md; driven by Gemini 3.1 Pro Preview's Dynamic-L4 crawl completing 2026-08-11). StableMut@K SD = 0.001-0.004 for most models (Qwen 1.5B an outlier at ~0.04). 3 of 6 N=4 pairs individually significant at raw p&lt;0.05; 1 survives Holm (pair 1-2, unchanged).</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>(a) N=4 headline rather than the approved N=5 - two of nine models could not reach N=5 (one by design, one quota-capped).
 (b) The approved H5 covers the WHOLE of RQ4, so RQ4.2-4.4 have no approved hypothesis and owe no test.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>THRESHOLD NOT MET - 0.583 is below the approved 0.7 criterion (only 1 of 6 N=4 pairs individually exceeds 0.7). Report the rank-level and score-level claims separately: score-level stability is strong, rank-level stability as specified is not met. Full per-pair breakdown: analysis/HYPOTHESIS_DEVIATIONS.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="105" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>H6 clause 1</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>RQ5</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Dynamic-benchmark mutation score will correlate POSITIVELY but IMPERFECTLY with code-generation Pass@1 on a proxy benchmark.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Pearson r and Spearman rho between scores.</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Dynamic &lt;-&gt; BigCodeBench, cross-family n_models=7: raw conditional Mut@K tau = 0.429 (not significant); coverage_adjusted tau = 0.905 (p=0.0034, survives Holm). The n=3 canonical 'perfect' correlation was a within-family size artefact.</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>The project's own later analysis plan added a pre-registered 0.4-0.8 'validity zone' that the approved H6 does not contain. Report both, but do not present the internal zone as if it were the approved criterion.</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>MIXED - positive under both metrics. 'Imperfect' holds for the raw metric; the coverage-adjusted correlation is close to perfect, which by the project's own internal criterion reads as near-redundant with a generic code-gen leaderboard.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>H6 clause 1</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>RQ5</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Dynamic-benchmark mutation score will correlate POSITIVELY but IMPERFECTLY with code-generation Pass@1 on a proxy benchmark.</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Pearson r and Spearman rho between scores.</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Dynamic &lt;-&gt; BigCodeBench, cross-family n_models=7: raw conditional Mut@K tau = 0.429 (not significant); coverage_adjusted tau = 0.905 (p=0.0034, survives Holm). The n=3 canonical 'perfect' correlation was a within-family size artefact.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>The project's own later analysis plan added a pre-registered 0.4-0.8 'validity zone' that the approved H6 does not contain. Report both, but do not present the internal zone as if it were the approved criterion.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>MIXED - positive under both metrics. 'Imperfect' holds for the raw metric; the coverage-adjusted correlation is close to perfect, which by the project's own internal criterion reads as near-redundant with a generic code-gen leaderboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
           <t>H6 clause 2</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>RQ5</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>The dynamic-proxy correlation will be WEAKER than the static-proxy correlation.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Pearson r and Spearman rho between scores (no Fisher z-test is required by the approved wording).</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Answerable from data already on disk: Dynamic &lt;-&gt; BigCodeBench tau = 0.905 vs ULT &lt;-&gt; BigCodeBench tau = 0.714 (coverage-adjusted, n_models=7); 0.429 vs 0.238 (raw conditional Mut@K).</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Written up 2026-08-12 (analysis/RQ5_INTERPRETATION.md's new "H6 clause 2" section, analysis/HYPOTHESIS_DEVIATIONS.md). Full 12-row table: Pearson/Spearman/Kendall, raw + coverage-adjusted, n=3 canonical + n=7 cross-family, with CIs.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>NOT SUPPORTED - the dynamic correlation is the STRONGER (or tied) one in all 12 scope/metric/statistic combinations tested, never weaker. Defensible as a favourable finding: the dynamic benchmark tracks external capability at least as well as, and often better than, the static one.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>NOT PURSUED - a later expanded hypothesis set (H4a, H4b, and separate hypotheses for RQ4.2/4.3/4.4) was drafted but NEVER submitted to or approved by the supervisor. It creates no obligation and is recorded here only for the audit trail. Nothing below appears in the paper. Recorded in PROJECT_BRIEF.md §11 as "drafted, not submitted, not pursued", 2026-08-12.</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="18" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>H4a (draft)</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>RQ3</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Tier-stratified inflation from fine-tuning on ONE dynamic instantiation would be larger at L1-L2 than L3-L4.</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Tier-stratified DiD + interaction term.</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Not run.</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Never approved. The supplementary memorisation study happens to have produced similar data, but no hypothesis obliges its analysis.</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>NOT PURSUED - out of scope for the approved set.</t>
-        </is>
-      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="18" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>H4b (draft)</t>
+          <t>H4a (draft)</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Within the CC&gt;=8 overlap region, the (static - dynamic) gap shrinks as ULT's CC band increases.</t>
+          <t>Tier-stratified inflation from fine-tuning on ONE dynamic instantiation would be larger at L1-L2 than L3-L4.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Spearman rho of the gap against CC band.</t>
+          <t>Tier-stratified DiD + interaction term.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Never approved. Computable from existing CC bands, but low-powered (4 bands per model).</t>
+          <t>Never approved. The supplementary memorisation study happens to have produced similar data, but no hypothesis obliges its analysis.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1056,35 +1056,72 @@
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>H4b (draft)</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>RQ3</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Within the CC&gt;=8 overlap region, the (static - dynamic) gap shrinks as ULT's CC band increases.</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Spearman rho of the gap against CC band.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Not run.</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Never approved. Computable from existing CC bands, but low-powered (4 bands per model).</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>NOT PURSUED - out of scope for the approved set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
           <t>H6/H7/H8 (draft)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>RQ4.2-4.4</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Separate hypotheses for within-family scaling (closed and open source) and provider effect at matched tier.</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Sign test / rank correlation / bootstrap CIs.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Not run as hypothesis tests; the underlying quantities are computable descriptively.</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Never approved. The approved H5 covers the whole of RQ4, so these sub-questions are descriptive by design, not demoted.</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>NOT PURSUED - reported descriptively only.</t>
         </is>
@@ -1092,7 +1129,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1926,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2178,188 +2215,188 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>H3 - tier gradient</t>
+          <t>H2-supplementary - post-hoc robustness replication (not part of the approved set)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Spearman rho, tier index vs Mut@K</t>
+          <t>Seen-vs-fresh instantiation baseline_pass_rate, per training source</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>n_models=9</t>
+          <t>n=150/instantiation, 6 conditions (2 sizes x 3 sources)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>All 9 models show a significant negative gradient; effect strengthens for 3/9, weakens for 5/9 when L1 is excluded (still significant for all 8 computable). Literal 'never goes back up' clause holds for 7/9 models exactly.</t>
+          <t>Self-contamination gap 8.7pp (1.5B) / 4.7pp (7B); cross-model contamination gap 52.7pp (1.5B) / 68.0pp (7B); non-leaked control -2.3 to 2.3pp (noise)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>&lt;0.05 for all 9</t>
+          <t>n/a (no hypothesis test, descriptive comparison)</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Survives Holm in both families</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>SUPPORTED (trend). Literal "never goes back up" clause: 7/9 models exactly, 2/9 (GPT-5, GPT-5-mini) one sub-1pp L1-&gt;L2 rebound each -- analysis/H3_INTERPRETATION.md.</t>
+          <t>SUPPLEMENTARY (POST-HOC) - pattern holds under both training sources; non-leaked control shows no gap. Cross-model conditions show a held-out exec_rate decline the self-contamination conditions do not, partially confounding their gap with a capability cost.</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>H3_ANALYSIS_PLAN.md / H3 outputs</t>
+          <t>analysis/finetune_endpoint_table.csv, analysis/finetune_decline_table.csv</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>RQ3</t>
+          <t>RQ2</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>H4 - static-dynamic gap larger at L1-L2 than L3-L4</t>
+          <t>H3 - tier gradient</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Mixed-effects interaction (never built)</t>
+          <t>Spearman rho, tier index vs Mut@K</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>n_models=9</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>ULT/PLT contain no L1-L2 problems, so no static score exists at those tiers to form a gap with</t>
+          <t>All 9 models show a significant negative gradient; effect strengthens for 3/9, weakens for 5/9 when L1 is excluded (still significant for all 8 computable). Literal 'never goes back up' clause holds for 7/9 models exactly.</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>&lt;0.05 for all 9</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>DROPPED - untestable by construction. Supervisor sign-off 2026-08-05.</t>
+          <t>Survives Holm in both families</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>SUPPORTED (trend). Literal "never goes back up" clause: 7/9 models exactly, 2/9 (GPT-5, GPT-5-mini) one sub-1pp L1-&gt;L2 rebound each -- analysis/H3_INTERPRETATION.md.</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>H4_DESIGN_MEMO.md</t>
+          <t>H3_ANALYSIS_PLAN.md / H3 outputs</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>RQ4</t>
+          <t>RQ3</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>H5 - ranking stability across instantiations</t>
+          <t>H4 - static-dynamic gap larger at L1-L2 than L3-L4</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Pairwise Kendall tau; StableMut@K mean + SD</t>
+          <t>Mixed-effects interaction (never built)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>N=4 scope; n_models 7-9 per pair</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Mean pairwise tau = 0.583 (approved threshold: &gt;0.7; corrected 2026-08-12 from a stale 0.667, analysis/WORKBOOK_VERIFICATION.md). StableMut@K SD = 0.001-0.004 for most models. 3 of 6 N=4 pairs individually significant at raw p&lt;0.05.</t>
+          <t>ULT/PLT contain no L1-L2 problems, so no static score exists at those tiers to form a gap with</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>&lt;0.05 for 3/6 pairs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>1 of 6 survives (pair 1-2, adjusted p=0.0015)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>THRESHOLD NOT MET at the rank level. Score-level stability strong - report the two claims separately.</t>
+          <t>DROPPED - untestable by construction. Supervisor sign-off 2026-08-05.</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>STABILITY.md / STABILITY_INTERPRETATION.md</t>
+          <t>H4_DESIGN_MEMO.md</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>RQ5</t>
+          <t>RQ4</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>H6 clause 1 - positive but imperfect correlation with proxy Pass@1</t>
+          <t>H5 - ranking stability across instantiations</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Kendall tau / Spearman rho / Pearson r + permutation p</t>
+          <t>Pairwise Kendall tau; StableMut@K mean + SD</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>n_models=7 cross-family (3 canonical)</t>
+          <t>N=4 scope; n_models 7-9 per pair</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>raw conditional Mut@K tau = 0.429 (not significant); coverage_adjusted tau = 0.905</t>
+          <t>Mean pairwise tau = 0.583 (approved threshold: &gt;0.7; corrected 2026-08-12 from a stale 0.667, analysis/WORKBOOK_VERIFICATION.md). StableMut@K SD = 0.001-0.004 for most models. 3 of 6 N=4 pairs individually significant at raw p&lt;0.05.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>0.0034 (adjusted metric)</t>
+          <t>&lt;0.05 for 3/6 pairs</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Survives Holm (adjusted metric)</t>
+          <t>1 of 6 survives (pair 1-2, adjusted p=0.0015)</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>MIXED - positive under both metrics; 'imperfect' holds for the raw metric, while the coverage-adjusted value is near-perfect.</t>
+          <t>THRESHOLD NOT MET at the rank level. Score-level stability strong - report the two claims separately.</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>RQ5_CROSS_FAMILY_PROVENANCE.md</t>
+          <t>STABILITY.md / STABILITY_INTERPRETATION.md</t>
         </is>
       </c>
     </row>
@@ -2371,37 +2408,37 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>H6 clause 2 - is the dynamic-proxy correlation WEAKER than static-proxy?</t>
+          <t>H6 clause 1 - positive but imperfect correlation with proxy Pass@1</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Direct comparison of the two correlations (approved wording requires no Fisher z)</t>
+          <t>Kendall tau / Spearman rho / Pearson r + permutation p</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>n_models=7</t>
+          <t>n_models=7 cross-family (3 canonical)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Dynamic&lt;-&gt;BigCodeBench tau = 0.905 vs ULT&lt;-&gt;BigCodeBench tau = 0.714 (coverage-adjusted); 0.429 vs 0.238 (raw). Dynamic is STRONGER under every statistic.</t>
+          <t>raw conditional Mut@K tau = 0.429 (not significant); coverage_adjusted tau = 0.905</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>already computed</t>
+          <t>0.0034 (adjusted metric)</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Survives Holm (adjusted metric)</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>NOT SUPPORTED - direction is opposite to the prediction across all 12 scope/metric/statistic combinations tested. Defensible as a favourable finding. Written up: analysis/RQ5_INTERPRETATION.md.</t>
+          <t>MIXED - positive under both metrics; 'imperfect' holds for the raw metric, while the coverage-adjusted value is near-perfect.</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -2418,40 +2455,87 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
+          <t>H6 clause 2 - is the dynamic-proxy correlation WEAKER than static-proxy?</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Direct comparison of the two correlations (approved wording requires no Fisher z)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>n_models=7</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Dynamic&lt;-&gt;BigCodeBench tau = 0.905 vs ULT&lt;-&gt;BigCodeBench tau = 0.714 (coverage-adjusted); 0.429 vs 0.238 (raw). Dynamic is STRONGER under every statistic.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>already computed</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>NOT SUPPORTED - direction is opposite to the prediction across all 12 scope/metric/statistic combinations tested. Defensible as a favourable finding. Written up: analysis/RQ5_INTERPRETATION.md.</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>RQ5_CROSS_FAMILY_PROVENANCE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>RQ5</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
           <t>Decomposition - what the agreement is actually made of (supporting analysis)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Kendall tau on each component</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>n_models=9</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>baseline_pass_rate ALONE = 0.889; conditional Mut@K alone = 0.278 Kendall tau (corrected 2026-08-12 from a stale 0.333, which was accurate as of 2026-08-07 but has since drifted -- 0.333 is now that same pair's Spearman rho instead); combined coverage_adjusted = 0.944</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Not a hypothesis test, but the single most important scoping finding in RQ5: the agreement is about WHETHER a model can produce a passing suite, not how good the tests are.</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>RQ5_DIAGNOSTICS.md</t>
         </is>

--- a/docs/Research_questions.xlsx
+++ b/docs/Research_questions.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>SUPPLEMENTARY - pattern holds under both self- and cross-model contamination: trained-instantiation scores rise, fresh-instantiation scores do not, at both model sizes. Non-leaked control shows no such gap. Strengthens H2's second-clause reading that memorisation binds to the leaked artefact, not the benchmark.</t>
+          <t>SUPPORTED (POST-HOC) - pattern holds under both self- and cross-model contamination: trained-instantiation scores rise, fresh-instantiation scores do not, at both model sizes. Non-leaked control shows no such gap. Strengthens H2's second-clause reading that memorisation binds to the leaked artefact, not the benchmark.</t>
         </is>
       </c>
     </row>
